--- a/01_Output/Final_Allocation_Emp_View.xlsx
+++ b/01_Output/Final_Allocation_Emp_View.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,105 +458,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Office Work</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aaron* Dorrance</t>
+          <t>AJ # Alkhamees</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aaron* Dorrance</t>
+          <t>AJ # Alkhamees</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana* Gonzalez</t>
+          <t>Aaron* Dorrance</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>5:30PM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ana* Gonzalez</t>
+          <t>Aaron* Dorrance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
@@ -568,61 +568,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anahi Guitierrez</t>
+          <t>Ana* Gonzalez</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anahi Guitierrez</t>
+          <t>Ana* Gonzalez</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
@@ -634,39 +634,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analuisa Flores Teran</t>
+          <t>Anahi Guitierrez</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>2:30PM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>5:00PM</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,29 +776,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Andrew (AJ) # Bowlen</t>
+          <t>Calvin # Levy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,29 +1018,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cassidy Sylves</t>
+          <t>Cristian Andrade</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cristian Andrade</t>
+          <t>Dev Mahajan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>12:30PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>1:00PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1:30PM</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Elizabeth Jurry</t>
+          <t>Ellia* Bono</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1370,51 +1370,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ethan Palmer</t>
+          <t>Finn Broderick</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ethan Palmer</t>
+          <t>Finn Broderick</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
     </row>
@@ -1426,24 +1426,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Finn Broderick</t>
+          <t>Hanah # Wilkins</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
     </row>
@@ -1475,78 +1475,78 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hanah # Wilkins</t>
+          <t>Joaquin Mendoza</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>12:00PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>12:30PM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hanah # Wilkins</t>
+          <t>Joaquin Mendoza</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>12:00PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>12:30PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1:00PM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hanah # Wilkins</t>
+          <t>Joaquin Mendoza</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>12:30PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>1:00PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2:30PM</t>
         </is>
       </c>
     </row>
@@ -1558,83 +1558,83 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Joaquin Mendoza</t>
+          <t>Joaquin Salinas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Joaquin Mendoza</t>
+          <t>Josiah Galvan-Lewis</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Joaquin Salinas</t>
+          <t>Josiah Galvan-Lewis</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
@@ -1646,34 +1646,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Josiah Galvan-Lewis</t>
+          <t>Kaeden Stander</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1685,66 +1685,66 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Josiah Galvan-Lewis</t>
+          <t>Kayhaan Rashiq</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kaeden Stander</t>
+          <t>Kayhaan Rashiq</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kayhaan Rashiq</t>
+          <t>Kevin^ Jenkins</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:30PM</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
     </row>
@@ -1800,34 +1800,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kevin^ Jenkins</t>
+          <t>Lauren* Koski</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1839,44 +1839,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kevin^ Jenkins</t>
+          <t>Lohith Ramesh</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lauren* Koski</t>
+          <t>Lohith Ramesh</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
@@ -1888,39 +1888,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lohith Ramesh</t>
+          <t>Luke* Ruhl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
     </row>
@@ -1932,29 +1932,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Luke* Ruhl</t>
+          <t>Lulu (Lyndsey)* Arterburn</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1964,85 +1964,85 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Luke* Ruhl</t>
+          <t>Madelyn* Ozdarski</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Lulu (Lyndsey)* Arterburn</t>
+          <t>Madelyn* Ozdarski</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lulu (Lyndsey)* Arterburn</t>
+          <t>Madelyn* Ozdarski</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lulu (Lyndsey)* Arterburn</t>
+          <t>Mali Chavez</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lulu (Lyndsey)* Arterburn</t>
+          <t>Mali Chavez</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2081,95 +2081,95 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Madelyn* Ozdarski</t>
+          <t>Mariana Cepeda</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Madelyn* Ozdarski</t>
+          <t>Mariana Cepeda</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>2:00PM</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>5:30PM</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Madelyn* Ozdarski</t>
+          <t>Marsailles Wesley</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mali Chavez</t>
+          <t>Marsailles Wesley</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mariana Cepeda</t>
+          <t>Miguel Tanner</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2179,19 +2179,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mariana Cepeda</t>
+          <t>Naman Talwar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2201,90 +2201,90 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mariana Cepeda</t>
+          <t>Naman Talwar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Marsailles Wesley</t>
+          <t>Ricardo Gomez</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Register Upstair</t>
+          <t>Register Downstair</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marsailles Wesley</t>
+          <t>Ricardo Gomez</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Greeter Downstair</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>11:00AM</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>12:00PM</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Miguel Tanner</t>
+          <t>Ricardo Gomez</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2294,256 +2294,256 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Naman Talwar</t>
+          <t>Saaijeesh Sottalu Naresh</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Naman Talwar</t>
+          <t>Saaijeesh Sottalu Naresh</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Naman Talwar</t>
+          <t>Saaijeesh Sottalu Naresh</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ricardo Gomez</t>
+          <t>Saaijeesh Sottalu Naresh</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Register Upstair</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ricardo Gomez</t>
+          <t>Scott Hackney</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Greeter Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ricardo Gomez</t>
+          <t>Scott Hackney</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Salesfloor Upstair</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Saaijeesh Sottalu Naresh</t>
+          <t>Scott Hackney</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Saaijeesh Sottalu Naresh</t>
+          <t>Serenity* Munoz</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Saaijeesh Sottalu Naresh</t>
+          <t>Serenity* Munoz</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Scott Hackney</t>
+          <t>Serenity* Munoz</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Scott Hackney</t>
+          <t>Shri Ram Gudipati</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2:30PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Scott Hackney</t>
+          <t>Solymar Kneale</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2553,230 +2553,142 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Serenity* Munoz</t>
+          <t>Solymar Kneale</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Register Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Serenity* Munoz</t>
+          <t>Solymar Kneale</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Serenity* Munoz</t>
+          <t>Summer Sutton</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>2:00PM</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Solymar Kneale</t>
+          <t>Summer Sutton</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Salesfloor Downstair</t>
+          <t>Greeter Upstair</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>2:00PM</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>2:30PM</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Solymar Kneale</t>
+          <t>Summer Sutton</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Greeter Upstair</t>
+          <t>Salesfloor Downstair</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>2:30PM</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Solymar Kneale</t>
+          <t>Zadie Knapp</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Salesfloor Upstair</t>
+          <t>Stockroom</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
-        <is>
-          <t>1:30PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Summer Sutton</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Salesfloor Downstair</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1:30PM</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2:30PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Summer Sutton</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Greeter Downstair</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2:30PM</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Zadie Knapp</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Salesfloor Downstair</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Zadie Knapp</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Greeter Downstair</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
         <is>
           <t>4:30PM</t>
         </is>
